--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProElementAdj001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProElementAdj001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -21,55 +21,55 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
-    <t>产品登记编码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>子产品代码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>此产品要素调整描述文字1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>此产品要素调整描述文字2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>调整要素</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>调整前</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>调整后</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>生效时间</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>调整此要素（补充说明文1）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>调整此要素（补充说明文2）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>报告发布日期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>调整此产品要素原因</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>对此要素调整(原因)</t>
+    <t>产品登记编码*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>子产品代码*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>报告发布日期（YYYY-MM-DD)*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>此产品要素调整（补充性）描述文字1【注：一产多要素时必填，一要素多产非必填】</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>此产品要素调整（补充性）描述文字2【注：一产多要素时必填，一要素多产非必填】</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>调整要素*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>调整前*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>调整后*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>生效时间（YYYY-MM-DD)*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>对此要素调整（原因）【注：一要素多产必填，一产多要素时非必填，】</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>调整此要素（补充说明文1）【注：一要素多产必填，一产多要素时非必填，】</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>调整此要素（补充说明文2）【注：一要素多产必填，一产多要素时非必填，】</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -481,49 +481,50 @@
   <cols>
     <col min="1" max="1" width="18.453125" style="1" customWidth="1"/>
     <col min="2" max="3" width="22.26953125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.26953125" customWidth="1"/>
     <col min="9" max="9" width="10.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="56" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="140" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProElementAdj001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProElementAdj001.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24180" windowHeight="13070"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24180" windowHeight="13065"/>
   </bookViews>
   <sheets>
     <sheet name="产品要素调整信息" sheetId="1" r:id="rId1"/>
@@ -33,10 +33,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>报告发布日期（YYYY-MM-DD)*</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>此产品要素调整（补充性）描述文字1【注：一产多要素时必填，一要素多产非必填】</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -57,10 +53,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>生效时间（YYYY-MM-DD)*</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>对此要素调整（原因）【注：一要素多产必填，一产多要素时非必填，】</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -70,6 +62,14 @@
   </si>
   <si>
     <t>调整此要素（补充说明文2）【注：一要素多产必填，一产多要素时非必填，】</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>生效时间（YYYY/MM/DD)*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>报告发布日期（YYYY/MM/DD)*</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -477,16 +477,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="18.453125" style="1" customWidth="1"/>
-    <col min="2" max="3" width="22.26953125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.26953125" customWidth="1"/>
-    <col min="9" max="9" width="10.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5" style="1" customWidth="1"/>
+    <col min="2" max="3" width="22.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.25" customWidth="1"/>
+    <col min="9" max="9" width="10.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.375" customWidth="1"/>
     <col min="13" max="13" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="140" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="135" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -494,37 +495,37 @@
         <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProElementAdj001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProElementAdj001.xlsx
@@ -156,7 +156,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -170,6 +170,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -480,10 +489,11 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="18.5" style="1" customWidth="1"/>
-    <col min="2" max="3" width="22.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22.25" style="6" customWidth="1"/>
     <col min="4" max="4" width="17.25" customWidth="1"/>
     <col min="9" max="9" width="10.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.375" customWidth="1"/>
+    <col min="10" max="10" width="12.375" style="6" customWidth="1"/>
     <col min="13" max="13" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -494,7 +504,7 @@
       <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D1" s="3" t="s">
@@ -515,7 +525,7 @@
       <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="7" t="s">
         <v>11</v>
       </c>
       <c r="K1" s="4" t="s">

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProElementAdj001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProElementAdj001.xlsx
@@ -21,10 +21,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
-    <t>调整此产品要素原因</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>产品登记编码*</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -33,14 +29,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>此产品要素调整（补充性）描述文字1【注：一产多要素时必填，一要素多产非必填】</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>此产品要素调整（补充性）描述文字2【注：一产多要素时必填，一要素多产非必填】</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>调整要素*</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -53,23 +41,34 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>对此要素调整（原因）【注：一要素多产必填，一产多要素时非必填，】</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>调整此要素（补充说明文1）【注：一要素多产必填，一产多要素时非必填，】</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>调整此要素（补充说明文2）【注：一要素多产必填，一产多要素时非必填，】</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>生效时间（YYYY/MM/DD)*</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>报告发布日期（YYYY/MM/DD)*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单产品多要素段1</t>
+  </si>
+  <si>
+    <t>单产品多要素段2【注：一产多要素时必填，一要素多产非必填】</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单产品多要素段3【注：一产多要素时必填，一要素多产非必填】</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单要素多产品段1【注：一要素多产必填，一产多要素时非必填，】</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单要素多产品段2【注：一要素多产必填，一产多要素时非必填，】</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单要素多产品段3【注：一要素多产必填，一产多要素时非必填，】</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -497,45 +496,45 @@
     <col min="13" max="13" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="135" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:13" ht="108" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="H1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
